--- a/JsonConverter/ExcelFiles/HeroSkill.xlsx
+++ b/JsonConverter/ExcelFiles/HeroSkill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\ACE\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4222DC-456C-4280-A1F7-27FE48B346C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9393E258-9F66-4875-A88A-B89C073B9BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="26940" windowHeight="13935" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HeroSkill" sheetId="1" r:id="rId1"/>
@@ -2318,7 +2318,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -2327,7 +2327,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="24">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M4" s="30" t="s">
         <v>79</v>
@@ -2777,7 +2777,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="24">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M5" s="30" t="s">
         <v>80</v>
@@ -2828,7 +2828,7 @@
         <v>2</v>
       </c>
       <c r="L6" s="24">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="M6" s="30" t="s">
         <v>81</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="22">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="M7" s="31" t="s">
         <v>82</v>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="22">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="M8" s="31" t="s">
         <v>83</v>
@@ -2981,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="22">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M9" s="31" t="s">
         <v>84</v>
@@ -3032,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="22">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="M10" s="32" t="s">
         <v>85</v>
@@ -3083,7 +3083,7 @@
         <v>2</v>
       </c>
       <c r="L11" s="22">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="M11" s="31" t="s">
         <v>86</v>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="22">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="M12" s="31" t="s">
         <v>87</v>
